--- a/etf_holdings/2026-10-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,52 +2187,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+1.14%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>695000</v>
+      </c>
       <c r="K31" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>1395000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>700,000</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-20_00992A_full_holdings.xlsx</t>
+          <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2242,150 +2260,186 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>367000</v>
+        <v>240000</v>
       </c>
       <c r="K32" t="n">
-        <v>567000</v>
+        <v>180000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-60,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-20_00992A_full_holdings.xlsx</t>
+          <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RECRUIT HOLDINGS CO LTD</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5.58%</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>6.28%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1097000</v>
+      </c>
       <c r="K33" t="n">
-        <v>88300</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>1197000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-20_00990A_full_holdings.xlsx</t>
+          <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASERTEC CORP</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.04%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-1.25%</t>
+        </is>
+      </c>
       <c r="J34" t="n">
-        <v>42900</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+        <v>539000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>389000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-150,000</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-20_00990A_full_holdings.xlsx</t>
+          <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2395,60 +2449,60 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>156000</v>
+        <v>387644</v>
       </c>
       <c r="K35" t="n">
-        <v>346000</v>
+        <v>267644</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>190,000</t>
+          <t>-120,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-20_00990A_full_holdings.xlsx</t>
+          <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2463,424 +2517,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>23000</v>
+        <v>528000</v>
       </c>
       <c r="K36" t="n">
-        <v>44000</v>
+        <v>608000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-10-20_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>+1.14%</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>695000</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1395000</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>700,000</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-10-20_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.56%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-0.72%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>240000</v>
-      </c>
-      <c r="K38" t="n">
-        <v>180000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-60,000</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-10-20_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>5.58%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>6.28%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>+0.70%</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>1097000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1197000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-10-20_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2.78%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-1.25%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>539000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>389000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-150,000</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-10-20_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>3.60%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-1.20%</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>387644</v>
-      </c>
-      <c r="K41" t="n">
-        <v>267644</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>-120,000</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-10-20_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>3.32%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.89%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>+0.57%</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>528000</v>
-      </c>
-      <c r="K42" t="n">
-        <v>608000</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
         <is>
           <t>2026-10-20_00407A_full_holdings.xlsx</t>
         </is>
